--- a/output/pdf_financials_xlsx/TSU.xlsx
+++ b/output/pdf_financials_xlsx/TSU.xlsx
@@ -4387,22 +4387,22 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-1.026</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-1.596</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-1.905</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-2.034</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-2.006</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-2.029</v>
       </c>
     </row>
     <row r="125">
@@ -4418,22 +4418,22 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-1.026</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-1.596</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-1.905</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-2.034</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-2.006</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-2.029</v>
       </c>
     </row>
     <row r="126">
@@ -10252,7 +10252,11 @@
           <t>Principal portion of lease payments</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -18248,7 +18252,7 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -18962,7 +18966,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E271" s="5" t="n">

--- a/output/pdf_financials_xlsx/TSU.xlsx
+++ b/output/pdf_financials_xlsx/TSU.xlsx
@@ -3868,10 +3868,10 @@
         <v>0</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>1.518</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>2.412</v>
       </c>
     </row>
     <row r="108">
@@ -4129,28 +4129,28 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-0.978</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-0.135</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-2.745</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.196</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-1.254</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.437</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.437</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.658</v>
       </c>
     </row>
     <row r="117">
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-7.782</v>
       </c>
     </row>
     <row r="122">
@@ -9396,7 +9396,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -9886,7 +9890,11 @@
           <t>Purchases of intangible assets</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>-0.978</v>
       </c>
@@ -10034,7 +10042,11 @@
           <t>Shares repurchased 15</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -11802,7 +11814,11 @@
           <t>Purchases of intangible assets 12</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -13016,7 +13032,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E157" s="5" t="n">
         <v>-0.342</v>
       </c>
